--- a/results/0916-all/四川盆地农林区/tech_selected_summary.xlsx
+++ b/results/0916-all/四川盆地农林区/tech_selected_summary.xlsx
@@ -355,538 +355,538 @@
     <t>自流井区</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>技术74</t>
-  </si>
-  <si>
-    <t>技术75</t>
-  </si>
-  <si>
-    <t>技术76</t>
-  </si>
-  <si>
-    <t>技术77</t>
-  </si>
-  <si>
-    <t>技术78</t>
-  </si>
-  <si>
-    <t>技术79</t>
-  </si>
-  <si>
-    <t>技术80</t>
-  </si>
-  <si>
-    <t>技术81</t>
-  </si>
-  <si>
-    <t>技术82</t>
-  </si>
-  <si>
-    <t>技术83</t>
-  </si>
-  <si>
-    <t>技术84</t>
-  </si>
-  <si>
-    <t>技术85</t>
-  </si>
-  <si>
-    <t>技术86</t>
-  </si>
-  <si>
-    <t>技术87</t>
-  </si>
-  <si>
-    <t>技术88</t>
-  </si>
-  <si>
-    <t>技术89</t>
-  </si>
-  <si>
-    <t>技术90</t>
-  </si>
-  <si>
-    <t>技术91</t>
-  </si>
-  <si>
-    <t>技术92</t>
-  </si>
-  <si>
-    <t>技术93</t>
-  </si>
-  <si>
-    <t>技术94</t>
-  </si>
-  <si>
-    <t>技术95</t>
-  </si>
-  <si>
-    <t>技术96</t>
-  </si>
-  <si>
-    <t>技术97</t>
-  </si>
-  <si>
-    <t>技术98</t>
-  </si>
-  <si>
-    <t>技术99</t>
-  </si>
-  <si>
-    <t>技术100</t>
-  </si>
-  <si>
-    <t>技术101</t>
-  </si>
-  <si>
-    <t>技术102</t>
-  </si>
-  <si>
-    <t>技术103</t>
-  </si>
-  <si>
-    <t>技术104</t>
-  </si>
-  <si>
-    <t>技术105</t>
-  </si>
-  <si>
-    <t>技术106</t>
-  </si>
-  <si>
-    <t>技术107</t>
-  </si>
-  <si>
-    <t>技术108</t>
-  </si>
-  <si>
-    <t>技术109</t>
-  </si>
-  <si>
-    <t>技术110</t>
-  </si>
-  <si>
-    <t>技术111</t>
-  </si>
-  <si>
-    <t>技术112</t>
-  </si>
-  <si>
-    <t>技术113</t>
-  </si>
-  <si>
-    <t>技术114</t>
-  </si>
-  <si>
-    <t>技术115</t>
-  </si>
-  <si>
-    <t>技术116</t>
-  </si>
-  <si>
-    <t>技术117</t>
-  </si>
-  <si>
-    <t>技术118</t>
-  </si>
-  <si>
-    <t>技术119</t>
-  </si>
-  <si>
-    <t>技术120</t>
-  </si>
-  <si>
-    <t>技术121</t>
-  </si>
-  <si>
-    <t>技术122</t>
-  </si>
-  <si>
-    <t>技术123</t>
-  </si>
-  <si>
-    <t>技术124</t>
-  </si>
-  <si>
-    <t>技术125</t>
-  </si>
-  <si>
-    <t>技术126</t>
-  </si>
-  <si>
-    <t>技术127</t>
-  </si>
-  <si>
-    <t>技术128</t>
-  </si>
-  <si>
-    <t>技术129</t>
-  </si>
-  <si>
-    <t>技术130</t>
-  </si>
-  <si>
-    <t>技术131</t>
-  </si>
-  <si>
-    <t>技术132</t>
-  </si>
-  <si>
-    <t>技术133</t>
-  </si>
-  <si>
-    <t>技术134</t>
-  </si>
-  <si>
-    <t>技术135</t>
-  </si>
-  <si>
-    <t>技术136</t>
-  </si>
-  <si>
-    <t>技术137</t>
-  </si>
-  <si>
-    <t>技术138</t>
-  </si>
-  <si>
-    <t>技术139</t>
-  </si>
-  <si>
-    <t>技术140</t>
-  </si>
-  <si>
-    <t>技术141</t>
-  </si>
-  <si>
-    <t>技术142</t>
-  </si>
-  <si>
-    <t>技术143</t>
-  </si>
-  <si>
-    <t>技术144</t>
-  </si>
-  <si>
-    <t>技术145</t>
-  </si>
-  <si>
-    <t>技术146</t>
-  </si>
-  <si>
-    <t>技术147</t>
-  </si>
-  <si>
-    <t>技术148</t>
-  </si>
-  <si>
-    <t>技术149</t>
-  </si>
-  <si>
-    <t>技术150</t>
-  </si>
-  <si>
-    <t>技术151</t>
-  </si>
-  <si>
-    <t>技术152</t>
-  </si>
-  <si>
-    <t>技术153</t>
-  </si>
-  <si>
-    <t>技术154</t>
-  </si>
-  <si>
-    <t>技术155</t>
-  </si>
-  <si>
-    <t>技术156</t>
-  </si>
-  <si>
-    <t>技术157</t>
-  </si>
-  <si>
-    <t>技术158</t>
-  </si>
-  <si>
-    <t>技术159</t>
-  </si>
-  <si>
-    <t>技术160</t>
-  </si>
-  <si>
-    <t>技术161</t>
-  </si>
-  <si>
-    <t>技术162</t>
-  </si>
-  <si>
-    <t>技术163</t>
-  </si>
-  <si>
-    <t>技术164</t>
-  </si>
-  <si>
-    <t>技术165</t>
-  </si>
-  <si>
-    <t>技术166</t>
-  </si>
-  <si>
-    <t>技术167</t>
-  </si>
-  <si>
-    <t>技术168</t>
-  </si>
-  <si>
-    <t>技术169</t>
-  </si>
-  <si>
-    <t>技术170</t>
-  </si>
-  <si>
-    <t>技术171</t>
-  </si>
-  <si>
-    <t>技术172</t>
-  </si>
-  <si>
-    <t>技术173</t>
-  </si>
-  <si>
-    <t>技术174</t>
-  </si>
-  <si>
-    <t>技术175</t>
-  </si>
-  <si>
-    <t>技术176</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Tech74</t>
+  </si>
+  <si>
+    <t>Tech75</t>
+  </si>
+  <si>
+    <t>Tech76</t>
+  </si>
+  <si>
+    <t>Tech77</t>
+  </si>
+  <si>
+    <t>Tech78</t>
+  </si>
+  <si>
+    <t>Tech79</t>
+  </si>
+  <si>
+    <t>Tech80</t>
+  </si>
+  <si>
+    <t>Tech81</t>
+  </si>
+  <si>
+    <t>Tech82</t>
+  </si>
+  <si>
+    <t>Tech83</t>
+  </si>
+  <si>
+    <t>Tech84</t>
+  </si>
+  <si>
+    <t>Tech85</t>
+  </si>
+  <si>
+    <t>Tech86</t>
+  </si>
+  <si>
+    <t>Tech87</t>
+  </si>
+  <si>
+    <t>Tech88</t>
+  </si>
+  <si>
+    <t>Tech89</t>
+  </si>
+  <si>
+    <t>Tech90</t>
+  </si>
+  <si>
+    <t>Tech91</t>
+  </si>
+  <si>
+    <t>Tech92</t>
+  </si>
+  <si>
+    <t>Tech93</t>
+  </si>
+  <si>
+    <t>Tech94</t>
+  </si>
+  <si>
+    <t>Tech95</t>
+  </si>
+  <si>
+    <t>Tech96</t>
+  </si>
+  <si>
+    <t>Tech97</t>
+  </si>
+  <si>
+    <t>Tech98</t>
+  </si>
+  <si>
+    <t>Tech99</t>
+  </si>
+  <si>
+    <t>Tech100</t>
+  </si>
+  <si>
+    <t>Tech101</t>
+  </si>
+  <si>
+    <t>Tech102</t>
+  </si>
+  <si>
+    <t>Tech103</t>
+  </si>
+  <si>
+    <t>Tech104</t>
+  </si>
+  <si>
+    <t>Tech105</t>
+  </si>
+  <si>
+    <t>Tech106</t>
+  </si>
+  <si>
+    <t>Tech107</t>
+  </si>
+  <si>
+    <t>Tech108</t>
+  </si>
+  <si>
+    <t>Tech109</t>
+  </si>
+  <si>
+    <t>Tech110</t>
+  </si>
+  <si>
+    <t>Tech111</t>
+  </si>
+  <si>
+    <t>Tech112</t>
+  </si>
+  <si>
+    <t>Tech113</t>
+  </si>
+  <si>
+    <t>Tech114</t>
+  </si>
+  <si>
+    <t>Tech115</t>
+  </si>
+  <si>
+    <t>Tech116</t>
+  </si>
+  <si>
+    <t>Tech117</t>
+  </si>
+  <si>
+    <t>Tech118</t>
+  </si>
+  <si>
+    <t>Tech119</t>
+  </si>
+  <si>
+    <t>Tech120</t>
+  </si>
+  <si>
+    <t>Tech121</t>
+  </si>
+  <si>
+    <t>Tech122</t>
+  </si>
+  <si>
+    <t>Tech123</t>
+  </si>
+  <si>
+    <t>Tech124</t>
+  </si>
+  <si>
+    <t>Tech125</t>
+  </si>
+  <si>
+    <t>Tech126</t>
+  </si>
+  <si>
+    <t>Tech127</t>
+  </si>
+  <si>
+    <t>Tech128</t>
+  </si>
+  <si>
+    <t>Tech129</t>
+  </si>
+  <si>
+    <t>Tech130</t>
+  </si>
+  <si>
+    <t>Tech131</t>
+  </si>
+  <si>
+    <t>Tech132</t>
+  </si>
+  <si>
+    <t>Tech133</t>
+  </si>
+  <si>
+    <t>Tech134</t>
+  </si>
+  <si>
+    <t>Tech135</t>
+  </si>
+  <si>
+    <t>Tech136</t>
+  </si>
+  <si>
+    <t>Tech137</t>
+  </si>
+  <si>
+    <t>Tech138</t>
+  </si>
+  <si>
+    <t>Tech139</t>
+  </si>
+  <si>
+    <t>Tech140</t>
+  </si>
+  <si>
+    <t>Tech141</t>
+  </si>
+  <si>
+    <t>Tech142</t>
+  </si>
+  <si>
+    <t>Tech143</t>
+  </si>
+  <si>
+    <t>Tech144</t>
+  </si>
+  <si>
+    <t>Tech145</t>
+  </si>
+  <si>
+    <t>Tech146</t>
+  </si>
+  <si>
+    <t>Tech147</t>
+  </si>
+  <si>
+    <t>Tech148</t>
+  </si>
+  <si>
+    <t>Tech149</t>
+  </si>
+  <si>
+    <t>Tech150</t>
+  </si>
+  <si>
+    <t>Tech151</t>
+  </si>
+  <si>
+    <t>Tech152</t>
+  </si>
+  <si>
+    <t>Tech153</t>
+  </si>
+  <si>
+    <t>Tech154</t>
+  </si>
+  <si>
+    <t>Tech155</t>
+  </si>
+  <si>
+    <t>Tech156</t>
+  </si>
+  <si>
+    <t>Tech157</t>
+  </si>
+  <si>
+    <t>Tech158</t>
+  </si>
+  <si>
+    <t>Tech159</t>
+  </si>
+  <si>
+    <t>Tech160</t>
+  </si>
+  <si>
+    <t>Tech161</t>
+  </si>
+  <si>
+    <t>Tech162</t>
+  </si>
+  <si>
+    <t>Tech163</t>
+  </si>
+  <si>
+    <t>Tech164</t>
+  </si>
+  <si>
+    <t>Tech165</t>
+  </si>
+  <si>
+    <t>Tech166</t>
+  </si>
+  <si>
+    <t>Tech167</t>
+  </si>
+  <si>
+    <t>Tech168</t>
+  </si>
+  <si>
+    <t>Tech169</t>
+  </si>
+  <si>
+    <t>Tech170</t>
+  </si>
+  <si>
+    <t>Tech171</t>
+  </si>
+  <si>
+    <t>Tech172</t>
+  </si>
+  <si>
+    <t>Tech173</t>
+  </si>
+  <si>
+    <t>Tech174</t>
+  </si>
+  <si>
+    <t>Tech175</t>
+  </si>
+  <si>
+    <t>Tech176</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -958,7 +958,7 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 160776633.58</t>
+    <t>160776633.58</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
@@ -1048,7 +1048,7 @@
     <t>4R(Right rate)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 563030367.80</t>
+    <t>563030367.80</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
@@ -1099,7 +1099,7 @@
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 365797772.98</t>
+    <t>365797772.98</t>
   </si>
   <si>
     <t>Slatted floor vs Solid floor_sheep&amp;goat</t>
@@ -1129,10 +1129,10 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 522972854.83</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>522972854.83</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -1141,10 +1141,10 @@
     <t>residue rerention_maize</t>
   </si>
   <si>
-    <t>总经济成本: 335742524.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 174000271.95</t>
+    <t>335742524.39</t>
+  </si>
+  <si>
+    <t>174000271.95</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -1162,13 +1162,13 @@
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 124902870.03</t>
+    <t>124902870.03</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 153253196.96</t>
+    <t>153253196.96</t>
   </si>
   <si>
     <t>Low protein diet_dairy</t>
@@ -1204,7 +1204,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 1643542800.33</t>
+    <t>1643542800.33</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -1273,10 +1273,10 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 173701579.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 137445669.22</t>
+    <t>173701579.16</t>
+  </si>
+  <si>
+    <t>137445669.22</t>
   </si>
   <si>
     <t>Low protein diet_beef cattle</t>
@@ -1354,7 +1354,7 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 1160243157.30</t>
+    <t>1160243157.30</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
@@ -1363,34 +1363,34 @@
     <t>compost（low）≤30%_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 1113515694.32</t>
-  </si>
-  <si>
-    <t>总经济成本: 58702829.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 231218276.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 527308054.58</t>
+    <t>1113515694.32</t>
+  </si>
+  <si>
+    <t>58702829.60</t>
+  </si>
+  <si>
+    <t>231218276.65</t>
+  </si>
+  <si>
+    <t>527308054.58</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_maize</t>
   </si>
   <si>
-    <t>总经济成本: 161236863.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 1200221.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 28565063.28</t>
-  </si>
-  <si>
-    <t>总经济成本: 1060148.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 173727511.50</t>
+    <t>161236863.99</t>
+  </si>
+  <si>
+    <t>1200221.00</t>
+  </si>
+  <si>
+    <t>28565063.28</t>
+  </si>
+  <si>
+    <t>1060148.00</t>
+  </si>
+  <si>
+    <t>173727511.50</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_rice</t>
@@ -1405,43 +1405,43 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 257944917.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 90915193.39</t>
+    <t>257944917.56</t>
+  </si>
+  <si>
+    <t>90915193.39</t>
   </si>
   <si>
     <t>manure（low）≤30%_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 479493557.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 92930354.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 137500864.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 78439920.82</t>
+    <t>479493557.25</t>
+  </si>
+  <si>
+    <t>92930354.10</t>
+  </si>
+  <si>
+    <t>137500864.73</t>
+  </si>
+  <si>
+    <t>78439920.82</t>
   </si>
   <si>
     <t>surface applied  plus irrigation _sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 667584128.73</t>
+    <t>667584128.73</t>
   </si>
   <si>
     <t>wooden lid cover_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 66051812.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 352419.88</t>
-  </si>
-  <si>
-    <t>总经济成本: 259050397.31</t>
+    <t>66051812.54</t>
+  </si>
+  <si>
+    <t>352419.88</t>
+  </si>
+  <si>
+    <t>259050397.31</t>
   </si>
   <si>
     <t>biochar_dairy</t>
@@ -1450,25 +1450,25 @@
     <t>band application_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 218388139.72</t>
-  </si>
-  <si>
-    <t>总经济成本: 142565678.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 180947947.58</t>
+    <t>218388139.72</t>
+  </si>
+  <si>
+    <t>142565678.60</t>
+  </si>
+  <si>
+    <t>180947947.58</t>
   </si>
   <si>
     <t>Acidification_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 988300670.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 275522889.50</t>
-  </si>
-  <si>
-    <t>总经济成本: 163304644.36</t>
+    <t>988300670.50</t>
+  </si>
+  <si>
+    <t>275522889.50</t>
+  </si>
+  <si>
+    <t>163304644.36</t>
   </si>
   <si>
     <t>compost（mid）30%-70%_vegetable</t>
@@ -1480,64 +1480,64 @@
     <t>Plant-derived N substitution_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 742815971.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 131599950.04</t>
-  </si>
-  <si>
-    <t>总经济成本: 208211652.68</t>
-  </si>
-  <si>
-    <t>总经济成本: 241779637.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 445286127.85</t>
+    <t>742815971.20</t>
+  </si>
+  <si>
+    <t>131599950.04</t>
+  </si>
+  <si>
+    <t>208211652.68</t>
+  </si>
+  <si>
+    <t>241779637.36</t>
+  </si>
+  <si>
+    <t>445286127.85</t>
   </si>
   <si>
     <t>Plant-derived N substitution_rice</t>
   </si>
   <si>
-    <t>总经济成本: 1163261209.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 643678476.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 193462485.20</t>
-  </si>
-  <si>
-    <t>总经济成本: 1009271274.92</t>
+    <t>1163261209.51</t>
+  </si>
+  <si>
+    <t>643678476.58</t>
+  </si>
+  <si>
+    <t>193462485.20</t>
+  </si>
+  <si>
+    <t>1009271274.92</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 522565911.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 171800605.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 7632198.06</t>
-  </si>
-  <si>
-    <t>总经济成本: 95750349.31</t>
+    <t>522565911.15</t>
+  </si>
+  <si>
+    <t>171800605.39</t>
+  </si>
+  <si>
+    <t>7632198.06</t>
+  </si>
+  <si>
+    <t>95750349.31</t>
   </si>
   <si>
     <t>Chemical amendments_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 621701196.91</t>
+    <t>621701196.91</t>
   </si>
   <si>
     <t>Cover_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 156071583.12</t>
-  </si>
-  <si>
-    <t>总经济成本: 167935755.98</t>
+    <t>156071583.12</t>
+  </si>
+  <si>
+    <t>167935755.98</t>
   </si>
   <si>
     <t>compost（high）≥70%_rice</t>
@@ -1546,67 +1546,67 @@
     <t>EEF(DI)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 271643580.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 382962134.05</t>
-  </si>
-  <si>
-    <t>总经济成本: 176585265.68</t>
+    <t>271643580.92</t>
+  </si>
+  <si>
+    <t>382962134.05</t>
+  </si>
+  <si>
+    <t>176585265.68</t>
   </si>
   <si>
     <t>Urease Inhibitor_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 180689349.58</t>
-  </si>
-  <si>
-    <t>总经济成本: 88753022.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 42965482.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 234975789.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 92968321.08</t>
-  </si>
-  <si>
-    <t>总经济成本: 1122931413.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 539509593.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 95553125.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 77934150.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 299577329.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 1602123260.94</t>
-  </si>
-  <si>
-    <t>总经济成本: 587708431.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 663492725.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 1968672972.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 64493292.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 831950813.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 134098684.45</t>
+    <t>180689349.58</t>
+  </si>
+  <si>
+    <t>88753022.54</t>
+  </si>
+  <si>
+    <t>42965482.25</t>
+  </si>
+  <si>
+    <t>234975789.07</t>
+  </si>
+  <si>
+    <t>92968321.08</t>
+  </si>
+  <si>
+    <t>1122931413.63</t>
+  </si>
+  <si>
+    <t>539509593.57</t>
+  </si>
+  <si>
+    <t>95553125.36</t>
+  </si>
+  <si>
+    <t>77934150.16</t>
+  </si>
+  <si>
+    <t>299577329.25</t>
+  </si>
+  <si>
+    <t>1602123260.94</t>
+  </si>
+  <si>
+    <t>587708431.56</t>
+  </si>
+  <si>
+    <t>663492725.56</t>
+  </si>
+  <si>
+    <t>1968672972.31</t>
+  </si>
+  <si>
+    <t>64493292.59</t>
+  </si>
+  <si>
+    <t>831950813.16</t>
+  </si>
+  <si>
+    <t>134098684.45</t>
   </si>
   <si>
     <t>Increasing concentrate level (grain)_dairy</t>
@@ -1642,37 +1642,37 @@
     <t>irrigation (water-saving irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 843791820.24</t>
-  </si>
-  <si>
-    <t>总经济成本: 128955686.36</t>
-  </si>
-  <si>
-    <t>总经济成本: 252832390.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 100522110.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 95484.16</t>
-  </si>
-  <si>
-    <t>总经济成本: 92773704.46</t>
-  </si>
-  <si>
-    <t>总经济成本: 369313443.37</t>
-  </si>
-  <si>
-    <t>总经济成本: 377285795.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 240175886.57</t>
-  </si>
-  <si>
-    <t>总经济成本: 105530491.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 1083494946.68</t>
+    <t>843791820.24</t>
+  </si>
+  <si>
+    <t>128955686.36</t>
+  </si>
+  <si>
+    <t>252832390.89</t>
+  </si>
+  <si>
+    <t>100522110.40</t>
+  </si>
+  <si>
+    <t>95484.16</t>
+  </si>
+  <si>
+    <t>92773704.46</t>
+  </si>
+  <si>
+    <t>369313443.37</t>
+  </si>
+  <si>
+    <t>377285795.60</t>
+  </si>
+  <si>
+    <t>240175886.57</t>
+  </si>
+  <si>
+    <t>105530491.59</t>
+  </si>
+  <si>
+    <t>1083494946.68</t>
   </si>
   <si>
     <t>Ventilation_beef cattle</t>
@@ -1687,28 +1687,28 @@
     <t>EEF(UI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 268235191.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 933173316.99</t>
-  </si>
-  <si>
-    <t>总经济成本: 192896876.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 429771745.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 16100330.20</t>
+    <t>268235191.79</t>
+  </si>
+  <si>
+    <t>933173316.99</t>
+  </si>
+  <si>
+    <t>192896876.85</t>
+  </si>
+  <si>
+    <t>429771745.10</t>
+  </si>
+  <si>
+    <t>16100330.20</t>
   </si>
   <si>
     <t>Oil_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 1922358598.10</t>
-  </si>
-  <si>
-    <t>总经济成本: 73573745.66</t>
+    <t>1922358598.10</t>
+  </si>
+  <si>
+    <t>73573745.66</t>
   </si>
   <si>
     <t>Ventilation_dairy</t>
@@ -1717,31 +1717,31 @@
     <t>surface applied  plus irrigation _poultry</t>
   </si>
   <si>
-    <t>总经济成本: 713867119.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 372227387.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 77888487.38</t>
+    <t>713867119.39</t>
+  </si>
+  <si>
+    <t>372227387.44</t>
+  </si>
+  <si>
+    <t>77888487.38</t>
   </si>
   <si>
     <t>Urease Inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 373283987.01</t>
-  </si>
-  <si>
-    <t>总经济成本: 243498313.24</t>
-  </si>
-  <si>
-    <t>总经济成本: 142307819.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 466692213.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 341154.62</t>
+    <t>373283987.01</t>
+  </si>
+  <si>
+    <t>243498313.24</t>
+  </si>
+  <si>
+    <t>142307819.52</t>
+  </si>
+  <si>
+    <t>466692213.51</t>
+  </si>
+  <si>
+    <t>341154.62</t>
   </si>
 </sst>
 </file>
